--- a/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T15:05:53+00:00</t>
+    <t>2026-09-14T06:56:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -879,7 +879,7 @@
     <t>Gibt an, mit welcher Gesamtdosis da Zielgebiet bestrahlt wurde (inklusive Boost).</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-strahlentherapie-strahlungseinheit</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-strahlentherapie-strahlungseinheit</t>
   </si>
   <si>
     <t>Procedure.extension:Gesamtdosis.value[x].id</t>
@@ -2299,7 +2299,7 @@
     <t>If the use case requires attributes from the BodySite resource (e.g. to identify and track separately) then use the standard extension [procedure-targetbodystructure](http://hl7.org/fhir/R4/extension-procedure-targetbodystructure.html).</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-strahlentherapie-zielgebiet</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-strahlentherapie-zielgebiet</t>
   </si>
   <si>
     <t>OBX-20</t>
@@ -2713,7 +2713,7 @@
     <t>Strahlenart der Bestrahlung gemäß 14.8 oBDS 2021.</t>
   </si>
   <si>
-    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-strahlentherapie-strahlenart</t>
+    <t>https://www.medizininformatik-initiative.de/fhir/ext/modul-onko/ValueSet/mii-vs-onko-strahlentherapie-strahlenart</t>
   </si>
   <si>
     <t>Procedure.usedCode:Strahlenart.id</t>
@@ -3132,7 +3132,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="84.54296875" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="94.171875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="96.11328125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.6640625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>

--- a/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot.rc3</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T06:56:03+00:00</t>
+    <t>2026-09-14T08:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc3</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T08:15:57+00:00</t>
+    <t>2026-10-14T15:44:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-14T15:44:38+00:00</t>
+    <t>2026-10-19T22:30:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
+++ b/branches/dev/StructureDefinition-mii-pr-onko-strahlentherapie-bestrahlung-strahlentherapie.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-19T22:30:48+00:00</t>
+    <t>2026-10-19T23:12:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
